--- a/Realistic_ER_Estimate/NTu/aggregate_Kipsigis_results.xlsx
+++ b/Realistic_ER_Estimate/NTu/aggregate_Kipsigis_results.xlsx
@@ -425,216 +425,472 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tea</t>
+          <t>Tea - SOC Baseline (tCO2e/ha)</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Tea - SOC Project (tCO2e/ha)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tea - ERs (tCO2e/ha)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="n">
+        <v>416.7166577479397</v>
+      </c>
+      <c r="B2" t="n">
+        <v>416.7161654532999</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>370.6452524762392</v>
+      </c>
+      <c r="B3" t="n">
+        <v>416.7161622645597</v>
+      </c>
+      <c r="C3" t="n">
         <v>46.07140208296041</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>346.4724625445878</v>
+      </c>
+      <c r="B4" t="n">
+        <v>416.7161593602667</v>
+      </c>
+      <c r="C4" t="n">
         <v>24.17278702735827</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>331.3496440312228</v>
+      </c>
+      <c r="B5" t="n">
+        <v>416.7161567150468</v>
+      </c>
+      <c r="C5" t="n">
         <v>15.12281586814519</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>321.0852874233717</v>
+      </c>
+      <c r="B6" t="n">
+        <v>416.71615430579</v>
+      </c>
+      <c r="C6" t="n">
         <v>10.26435419859433</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>313.5061686607335</v>
+      </c>
+      <c r="B7" t="n">
+        <v>416.7161521114476</v>
+      </c>
+      <c r="C7" t="n">
         <v>7.579116568295646</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>307.470872735565</v>
+      </c>
+      <c r="B8" t="n">
+        <v>416.7161501128483</v>
+      </c>
+      <c r="C8" t="n">
         <v>6.035293926569238</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>302.3730170425188</v>
+      </c>
+      <c r="B9" t="n">
+        <v>416.7161482925313</v>
+      </c>
+      <c r="C9" t="n">
         <v>5.097853872729203</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>297.8860995533674</v>
+      </c>
+      <c r="B10" t="n">
+        <v>416.716146634593</v>
+      </c>
+      <c r="C10" t="n">
         <v>4.486915831213115</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>293.8309128318953</v>
+      </c>
+      <c r="B11" t="n">
+        <v>416.7161451245489</v>
+      </c>
+      <c r="C11" t="n">
         <v>4.055185211428011</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>290.1061744912528</v>
+      </c>
+      <c r="B12" t="n">
+        <v>416.7161437492061</v>
+      </c>
+      <c r="C12" t="n">
         <v>3.724736965299755</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>286.6520811280893</v>
+      </c>
+      <c r="B13" t="n">
+        <v>416.7161424965486</v>
+      </c>
+      <c r="C13" t="n">
         <v>3.454092110506068</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
+        <v>283.4311051755478</v>
+      </c>
+      <c r="B14" t="n">
+        <v>416.7161413556326</v>
+      </c>
+      <c r="C14" t="n">
         <v>3.220974811625434</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>280.4178518654657</v>
+      </c>
+      <c r="B15" t="n">
+        <v>416.7161403164905</v>
+      </c>
+      <c r="C15" t="n">
         <v>3.013252270939949</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>277.5936862872925</v>
+      </c>
+      <c r="B16" t="n">
+        <v>416.7161393700435</v>
+      </c>
+      <c r="C16" t="n">
         <v>2.824164631726106</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>274.9438753953747</v>
+      </c>
+      <c r="B17" t="n">
+        <v>416.7161385080228</v>
+      </c>
+      <c r="C17" t="n">
         <v>2.649810029897173</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
+        <v>272.4560576138041</v>
+      </c>
+      <c r="B18" t="n">
+        <v>416.7161377228974</v>
+      </c>
+      <c r="C18" t="n">
         <v>2.48781699644527</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
+        <v>270.119414262706</v>
+      </c>
+      <c r="B19" t="n">
+        <v>416.7161370078083</v>
+      </c>
+      <c r="C19" t="n">
         <v>2.33664263600887</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>267.924212758152</v>
+      </c>
+      <c r="B20" t="n">
+        <v>416.7161363565076</v>
+      </c>
+      <c r="C20" t="n">
         <v>2.195200853253444</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>265.8615473951157</v>
+      </c>
+      <c r="B21" t="n">
+        <v>416.7161357633055</v>
+      </c>
+      <c r="C21" t="n">
         <v>2.062664769834166</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>263.9231857083969</v>
+      </c>
+      <c r="B22" t="n">
+        <v>416.7161352230189</v>
+      </c>
+      <c r="C22" t="n">
         <v>1.938361146432124</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
+        <v>262.1014717621024</v>
+      </c>
+      <c r="B23" t="n">
+        <v>416.7161347309275</v>
+      </c>
+      <c r="C23" t="n">
         <v>1.821713454203173</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
+        <v>260.3892605990413</v>
+      </c>
+      <c r="B24" t="n">
+        <v>416.7161342827328</v>
+      </c>
+      <c r="C24" t="n">
         <v>1.71221071486643</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
+        <v>258.7798701623282</v>
+      </c>
+      <c r="B25" t="n">
+        <v>416.7161338745187</v>
+      </c>
+      <c r="C25" t="n">
         <v>1.609390028498988</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
+        <v>257.267043384326</v>
+      </c>
+      <c r="B26" t="n">
+        <v>416.7161335027185</v>
+      </c>
+      <c r="C26" t="n">
         <v>1.51282640620208</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
+        <v>255.8449165137184</v>
+      </c>
+      <c r="B27" t="n">
+        <v>416.7161331640843</v>
+      </c>
+      <c r="C27" t="n">
         <v>1.422126531973281</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>254.5079915396254</v>
+      </c>
+      <c r="B28" t="n">
+        <v>416.7161328556575</v>
+      </c>
+      <c r="C28" t="n">
         <v>1.33692466566617</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
+        <v>253.2511115213355</v>
+      </c>
+      <c r="B29" t="n">
+        <v>416.7161325747434</v>
+      </c>
+      <c r="C29" t="n">
         <v>1.25687973737583</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
+        <v>252.0694381388006</v>
+      </c>
+      <c r="B30" t="n">
+        <v>416.7161323188877</v>
+      </c>
+      <c r="C30" t="n">
         <v>1.1816731266793</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
+        <v>250.9584310512001</v>
+      </c>
+      <c r="B31" t="n">
+        <v>416.7161320858555</v>
+      </c>
+      <c r="C31" t="n">
         <v>1.111006854568193</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
+        <v>249.9138287988659</v>
+      </c>
+      <c r="B32" t="n">
+        <v>416.7161318736105</v>
+      </c>
+      <c r="C32" t="n">
         <v>1.044602040089326</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
+        <v>248.9316310658566</v>
+      </c>
+      <c r="B33" t="n">
+        <v>416.7161316802985</v>
+      </c>
+      <c r="C33" t="n">
         <v>0.9821975396971302</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
+        <v>248.0080821672871</v>
+      </c>
+      <c r="B34" t="n">
+        <v>416.7161315042308</v>
+      </c>
+      <c r="C34" t="n">
         <v>0.9235487225018252</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
+        <v>247.1396556534173</v>
+      </c>
+      <c r="B35" t="n">
+        <v>416.7161313438687</v>
+      </c>
+      <c r="C35" t="n">
         <v>0.868426353507715</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>246.3230399401349</v>
+      </c>
+      <c r="B36" t="n">
+        <v>416.7161311978115</v>
+      </c>
+      <c r="C36" t="n">
         <v>0.8166155672252605</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
+        <v>245.5551248873981</v>
+      </c>
+      <c r="B37" t="n">
+        <v>416.7161310647832</v>
+      </c>
+      <c r="C37" t="n">
         <v>0.7679149197084882</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
+        <v>244.8329892559102</v>
+      </c>
+      <c r="B38" t="n">
+        <v>416.7161309436214</v>
+      </c>
+      <c r="C38" t="n">
         <v>0.7221355103260692</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
+        <v>244.1538889790727</v>
+      </c>
+      <c r="B39" t="n">
+        <v>416.716130833268</v>
+      </c>
+      <c r="C39" t="n">
         <v>0.6791001664841474</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
+        <v>243.5152461928332</v>
+      </c>
+      <c r="B40" t="n">
+        <v>416.7161307327582</v>
+      </c>
+      <c r="C40" t="n">
         <v>0.6386426857296451</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
+        <v>242.9146389708152</v>
+      </c>
+      <c r="B41" t="n">
+        <v>416.7161306412145</v>
+      </c>
+      <c r="C41" t="n">
         <v>0.6006071304743253</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
+        <v>242.3497917162907</v>
+      </c>
+      <c r="B42" t="n">
+        <v>416.7161305578367</v>
+      </c>
+      <c r="C42" t="n">
         <v>0.5648471711466575</v>
       </c>
     </row>
